--- a/presets/中国政法大学-本科毕业论文.xlsx
+++ b/presets/中国政法大学-本科毕业论文.xlsx
@@ -498,6 +498,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -657,6 +658,7 @@
       </c>
       <c r="C15" s="5" t="inlineStr"/>
     </row>
+    <row r="16"/>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
@@ -1533,7 +1535,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
@@ -3737,6 +3739,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr"/>
     </row>
+    <row r="51"/>
     <row r="52" ht="24" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
@@ -3831,6 +3834,7 @@
       <c r="F55" s="5" t="inlineStr"/>
       <c r="G55" s="4" t="inlineStr"/>
     </row>
+    <row r="56"/>
     <row r="57" ht="24" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
@@ -3872,6 +3876,7 @@
         </is>
       </c>
     </row>
+    <row r="60"/>
     <row r="61" ht="24" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
@@ -3961,6 +3966,7 @@
       </c>
       <c r="C67" s="5" t="inlineStr"/>
     </row>
+    <row r="68"/>
     <row r="69" ht="24" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
@@ -4002,6 +4008,7 @@
         </is>
       </c>
     </row>
+    <row r="72"/>
     <row r="73" ht="24" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
         <is>
@@ -4069,6 +4076,7 @@
         </is>
       </c>
     </row>
+    <row r="78"/>
     <row r="79" ht="24" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
         <is>
@@ -4157,7 +4165,7 @@
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>【关键词】</t>
+          <t xml:space="preserve">【关键词】  </t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr"/>
@@ -4229,7 +4237,7 @@
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>【KEYWORDS】</t>
+          <t xml:space="preserve">【KEYWORDS】  </t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
